--- a/槽波采集观测系统.xlsx
+++ b/槽波采集观测系统.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
   <si>
-    <t>炮号</t>
+    <t>检波器号</t>
   </si>
   <si>
     <t>X坐标</t>
@@ -41,7 +41,7 @@
     <t>高程m</t>
   </si>
   <si>
-    <t>检波器号</t>
+    <t>炮号</t>
   </si>
 </sst>
 </file>
